--- a/public/voorbeeld-artikelen.xlsx
+++ b/public/voorbeeld-artikelen.xlsx
@@ -498,10 +498,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Geen geldige waarde" error="Vul een getal groter dan 0 in." type="decimal" errorStyle="warning" operator="greaterThan">
+    <dataValidation sqref="B2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldige waarde" error="Vul een getal groter dan 0 in." type="decimal" errorStyle="warning" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Geen geldig aantal" error="Vul een geheel getal van minstens 1 in, of laat de cel leeg (= 1)." type="whole" errorStyle="warning" operator="greaterThanOrEqual">
+    <dataValidation sqref="F2:F10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldig aantal" error="Vul een geheel getal van minstens 1 in, of laat de cel leeg (= 1)." type="whole" errorStyle="warning" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/voorbeeld-artikelen.xlsx
+++ b/public/voorbeeld-artikelen.xlsx
@@ -455,7 +455,7 @@
     <col width="25" customWidth="1" style="2" min="3" max="3"/>
     <col width="24" customWidth="1" style="2" min="4" max="4"/>
     <col width="36" customWidth="1" style="3" min="5" max="5"/>
-    <col width="31" customWidth="1" style="2" min="6" max="6"/>
+    <col width="36" customWidth="1" style="2" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Aantal artikelen per binnendoos</t>
+          <t>Min. aantal artikelen per binnendoos</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -501,7 +501,7 @@
     <dataValidation sqref="B2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldige waarde" error="Vul een getal groter dan 0 in." type="decimal" errorStyle="warning" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldig aantal" error="Vul een geheel getal van minstens 1 in, of laat de cel leeg (= 1)." type="whole" errorStyle="warning" operator="greaterThanOrEqual">
+    <dataValidation sqref="F2:F10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldig aantal" error="Vul een geheel getal van minstens 1 in, of laat de cel leeg (= 2)." type="whole" errorStyle="warning" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -640,12 +640,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Aantal artikelen per binnendoos</t>
+          <t>Min. aantal artikelen per binnendoos</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Hoeveel artikelen er in één binnendoos zitten, als geheel getal. Mag leeg blijven: leeg = 1.</t>
+          <t>Hoeveel artikelen er minstens in één binnendoos zitten, als geheel getal. Mag leeg blijven: leeg = 2.</t>
         </is>
       </c>
     </row>

--- a/public/voorbeeld-artikelen.xlsx
+++ b/public/voorbeeld-artikelen.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artikelen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voorbeeld" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -455,8 +456,11 @@
     <col width="25" customWidth="1" style="2" min="3" max="3"/>
     <col width="24" customWidth="1" style="2" min="4" max="4"/>
     <col width="36" customWidth="1" style="3" min="5" max="5"/>
-    <col width="36" customWidth="1" style="2" min="6" max="6"/>
+    <col width="26" customWidth="1" style="2" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,7 +491,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Min. aantal artikelen per binnendoos</t>
+          <t>Artikelen per binnendoos</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
@@ -495,14 +499,32 @@
           <t>Omschrijving</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Kantelbaar (ja/nee)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>L mag verticaal (ja/nee)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>B mag verticaal (ja/nee)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B2:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldige waarde" error="Vul een getal groter dan 0 in." type="decimal" errorStyle="warning" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen geldig aantal" error="Vul een geheel getal van minstens 1 in, of laat de cel leeg (= 2)." type="whole" errorStyle="warning" operator="greaterThanOrEqual">
       <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:J10000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Geen ja of nee" error="Vul ja of nee in, of laat de cel leeg (= nee)." type="list" errorStyle="warning">
+      <formula1>"ja,nee"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -515,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -640,12 +662,12 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Min. aantal artikelen per binnendoos</t>
+          <t>Artikelen per binnendoos</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Hoeveel artikelen er minstens in één binnendoos zitten, als geheel getal. Mag leeg blijven: leeg = 2.</t>
+          <t>Hoeveel artikelen er in één binnendoos zitten, als geheel getal. Mag leeg blijven: leeg = 2.</t>
         </is>
       </c>
     </row>
@@ -666,52 +688,318 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Kantelbaar (ja/nee)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Ja als de binnendoos op zijn kant mag staan, anders nee. Mag leeg blijven: leeg = nee. Bij ja moet L of B (of allebei) verticaal mogen.</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>L mag verticaal (ja/nee)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Ja als de binnendoos zo mag staan dat de lengte verticaal is. Alleen bij kantelbaar ja. Leeg = nee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>B mag verticaal (ja/nee)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Ja als de binnendoos zo mag staan dat de breedte verticaal is. Alleen bij kantelbaar ja. Leeg = nee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Goed om te weten</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- Laat de eerste rij met de kolomnamen staan: de app herkent daaraan de kolommen en de eenheden. Vul vanaf rij 2 één artikel per rij in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- Lengtes in millimeters (mm), gewicht in kilogram (kg) inclusief inhoud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- De app kiest bij het importeren standaard het eerste werkblad (Artikelen).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- Een nieuw artikelnummer wordt als nieuw artikel aangemaakt. Een bestaand artikel wordt alleen overschreven als je de wijziging in de app bevestigt.</t>
+          <t>- Laat de eerste rij met de kolomnamen staan: de app herkent daaraan de kolommen en de eenheden. Vul vanaf rij 2 één artikel per rij in.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- Kantelbaar en welke as verticaal mag staan stel je daarna per artikel in op het tabblad Artikelen.</t>
+          <t>- Lengtes in millimeters (mm), gewicht in kilogram (kg) inclusief inhoud.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>- De app kiest bij het importeren standaard het eerste werkblad (Artikelen).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Een nieuw artikelnummer wordt als nieuw artikel aangemaakt. Een bestaand artikel wordt alleen overschreven als je de wijziging in de app bevestigt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Voor ja en nee mag ook: j en n, yes en no, x (= ja), 1 en 0, of waar en onwaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Laat je de kolom Kantelbaar weg, dan zijn nieuwe artikelen niet kantelbaar en blijven de kantelrechten van bestaande artikelen zoals ze zijn. Je kunt ze ook later per artikel aanpassen op het tabblad Artikelen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Het werkblad Voorbeeld toont drie ingevulde rijen. Vul je eigen artikelen in op het werkblad Artikelen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>- Importeren gaat via het tabblad Excel-import.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="1" min="1" max="1"/>
+    <col width="24" customWidth="1" style="2" min="2" max="2"/>
+    <col width="25" customWidth="1" style="2" min="3" max="3"/>
+    <col width="24" customWidth="1" style="2" min="4" max="4"/>
+    <col width="36" customWidth="1" style="3" min="5" max="5"/>
+    <col width="26" customWidth="1" style="2" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Artikelcode</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Lengte binnendoos (mm)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Breedte binnendoos (mm)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Hoogte binnendoos (mm)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Gewicht binnendoos incl. inhoud (kg)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Artikelen per binnendoos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Kantelbaar (ja/nee)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>L mag verticaal (ja/nee)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>B mag verticaal (ja/nee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VOORBEELD-1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kop en schotel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VOORBEELD-2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
+      </c>
+      <c r="C3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vaas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VOORBEELD-3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>350</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bordenset</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ja</t>
         </is>
       </c>
     </row>

--- a/public/voorbeeld-artikelen.xlsx
+++ b/public/voorbeeld-artikelen.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Ja als de binnendoos op zijn kant mag staan, anders nee. Mag leeg blijven: leeg = nee. Bij ja moet L of B (of allebei) verticaal mogen.</t>
+          <t>Ja als de binnendoos op zijn kant mag staan, anders nee. Mag leeg blijven: leeg = nee, tenzij bij L of B ja staat. Bij ja mogen L en B allebei verticaal, behalve als er bij L of B nee staat.</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Ja als de binnendoos zo mag staan dat de lengte verticaal is. Alleen bij kantelbaar ja. Leeg = nee.</t>
+          <t>Ja als de binnendoos zo mag staan dat de lengte verticaal is, nee als dat niet mag. Leeg = ja bij kantelbaar ja, anders nee.</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Ja als de binnendoos zo mag staan dat de breedte verticaal is. Alleen bij kantelbaar ja. Leeg = nee.</t>
+          <t>Ja als de binnendoos zo mag staan dat de breedte verticaal is, nee als dat niet mag. Leeg = ja bij kantelbaar ja, anders nee.</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Een nieuw artikelnummer wordt als nieuw artikel aangemaakt. Een bestaand artikel wordt alleen overschreven als je de wijziging in de app bevestigt.</t>
+          <t>- Een nieuw artikelnummer wordt als nieuw artikel aangemaakt. Een bestaand artikel wordt alleen overschreven als je de wijziging in de app bevestigt. Een rij met een fout wordt niet geïmporteerd; de app toont de fout per rij.</t>
         </is>
       </c>
     </row>
